--- a/EV/data/bilsalg.xlsx
+++ b/EV/data/bilsalg.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cicero.sharepoint.com/sites/Group-ClimateMitigation/Shared Documents/SmallJobs/2019/201903_bilsalg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="13_ncr:1_{86895BED-31D7-474B-A798-158E65269AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2FB4E43-C559-4378-81ED-EA66B3CED8B3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{94A590A3-A19D-4EDC-866B-407362CF22C8}"/>
   </bookViews>
